--- a/data/mau-file-import/mau_import_danh_muc_dich_vu.xlsx
+++ b/data/mau-file-import/mau_import_danh_muc_dich_vu.xlsx
@@ -1,146 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a092a069fd73f102/z.Database-TTKD-Data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_6857A9E30EAA37722FDB27BC17372765C1AA3EC3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E66BB01-C5A9-4282-8E53-B8528AE699BB}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="mapping-spdv" sheetId="1" r:id="rId1"/>
-    <sheet name="Huong_Dan" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
-  <si>
-    <t>nhom_chinh</t>
-  </si>
-  <si>
-    <t>ma_spdv</t>
-  </si>
-  <si>
-    <t>ten_spdv</t>
-  </si>
-  <si>
-    <t>nhom_dich_vu</t>
-  </si>
-  <si>
-    <t>ghi_chu</t>
-  </si>
-  <si>
-    <t>BCCP</t>
-  </si>
-  <si>
-    <t>Truyền thống</t>
-  </si>
-  <si>
-    <t>HƯỚNG DẪN BỔ SUNG SẢN PHẨM DỊCH VỤ MỚI</t>
-  </si>
-  <si>
-    <t>Bước 1: Sếp chuyển sang sheet đầu tiên (mapping-spdv).</t>
-  </si>
-  <si>
-    <t>Bước 2: Điền các mã sản phẩm dịch vụ mới vào dưới các dòng mẫu (Sếp có thể xóa 2 dòng mẫu nền xám nếu muốn).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - nhom_chinh: Điền 'BCCP' hoặc 'HCC'</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - ma_spdv: Mã dịch vụ mới phát sinh (ví dụ: CTN032)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - ten_spdv: Tên gọi dịch vụ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - nhom_dich_vu: Điền đúng một trong các chữ: 'Truyền thống', 'TMĐT', 'Quốc tế' hoặc 'Hành chính công'</t>
-  </si>
-  <si>
-    <t>Bước 3: Chọn sheet 'mapping-spdv', bấm File -&gt; Save As trên Excel.</t>
-  </si>
-  <si>
-    <t>Bước 4: Chọn định dạng lưu là 'CSV UTF-8 (Comma delimited) (*.csv)'. Bấm Save.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   - Lưu ý: Excel sẽ hiện cảnh báo chỉ lưu sheet đang chọn (mapping-spdv) sang CSV, Sếp bấm OK/Yes.</t>
-  </si>
-  <si>
-    <t>Bước 5: Tải file CSV vừa lưu lên khu vực 'Quản lý Danh mục Dịch vụ' ở cuối trang Nhập dữ liệu trên Dashboard.</t>
-  </si>
-  <si>
-    <t>Bước 6: Bấm nút 'Đồng bộ danh mục Dịch vụ' để hệ thống tự động cập nhật.</t>
-  </si>
-  <si>
-    <t>CTN052</t>
-  </si>
-  <si>
-    <t>Chuyển phát nhanh hàng nông sản</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF1E3A8A"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E3A8A"/>
-        <bgColor rgb="FF1E3A8A"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1F5F9"/>
-        <bgColor rgb="FFF1F5F9"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -148,52 +42,85 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCBD5E1"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFCBD5E1"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFCBD5E1"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFCBD5E1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -481,126 +408,78 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="39" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ma_spdv</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ten_spdv</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Loại dịch vụ</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>BK/E</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="3"/>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CTN052</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Chuyển phát nhanh hàng nông sản</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Truyền thống</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BK</t>
+        </is>
+      </c>
     </row>
-    <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="3"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="100" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
-        <v>18</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ETN001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>EMS Premium Tài liệu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Truyền thống</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EMS</t>
+        </is>
       </c>
     </row>
   </sheetData>
